--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA9B7DB4-EC11-4D92-AFB2-067C7EE0AB05}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="11_284323B7179BCE1E4FF04B89F2162C28D8426764" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C962663-0C12-4072-8909-80C32C70FCBE}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11895" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -131,121 +131,121 @@
     <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
   </si>
   <si>
-    <t>Arroz con quinoa</t>
-  </si>
-  <si>
-    <t>31 ago</t>
-  </si>
-  <si>
-    <t>1 sept</t>
-  </si>
-  <si>
-    <t>2 sept</t>
-  </si>
-  <si>
-    <t>3 sept</t>
-  </si>
-  <si>
-    <t>4 sept</t>
-  </si>
-  <si>
-    <t>5 sept</t>
-  </si>
-  <si>
-    <t>6 sept</t>
-  </si>
-  <si>
-    <t>Sopa de cuchuco de cebada</t>
-  </si>
-  <si>
-    <t>Costilla de cerdo en salsa BBQ</t>
-  </si>
-  <si>
-    <t>Papa asada</t>
-  </si>
-  <si>
-    <t>Verduras salteadas</t>
-  </si>
-  <si>
-    <t>Sopa de verduras</t>
-  </si>
-  <si>
-    <t>Pollo a la broaster</t>
-  </si>
-  <si>
-    <t>Papas horneadas al limón</t>
-  </si>
-  <si>
-    <t>Ensalada hawaiana</t>
-  </si>
-  <si>
-    <t>Arroz al cebollín</t>
-  </si>
-  <si>
-    <t>Crema de tomate</t>
-  </si>
-  <si>
-    <t>Tacos de carne desmechada</t>
-  </si>
-  <si>
-    <t>Fríjoles</t>
-  </si>
-  <si>
-    <t>Guacamole - Ensalada pico e gallo</t>
-  </si>
-  <si>
-    <t>Arroz amarillo</t>
-  </si>
-  <si>
-    <t>Sopa de avena</t>
-  </si>
-  <si>
-    <t>Pollo tropical</t>
-  </si>
-  <si>
-    <t>Dedito de queso mozzarella</t>
-  </si>
-  <si>
-    <t>Ensalada florentina</t>
-  </si>
-  <si>
-    <t>Sopa de arracacha</t>
-  </si>
-  <si>
-    <t>Bolitas de res en salsa napolitana</t>
-  </si>
-  <si>
-    <t>Yuca dorada</t>
-  </si>
-  <si>
-    <t>Soufflé de acelgas</t>
-  </si>
-  <si>
-    <t>Pollo a la jardinera</t>
-  </si>
-  <si>
-    <t>Torta de banano</t>
-  </si>
-  <si>
-    <t>Ensalada de pepino cohombro, tomate y zuchinni</t>
-  </si>
-  <si>
-    <t>a la vinagreta</t>
-  </si>
-  <si>
-    <t>Entero</t>
-  </si>
-  <si>
-    <t>Consomé</t>
-  </si>
-  <si>
-    <t>Costilla de res</t>
-  </si>
-  <si>
-    <t>Yuca, plátano y mazorca</t>
-  </si>
-  <si>
-    <t>Guacamole - Arroz blanco</t>
+    <t>7 sept</t>
+  </si>
+  <si>
+    <t>8 sept</t>
+  </si>
+  <si>
+    <t>9 sept</t>
+  </si>
+  <si>
+    <t>10 sept</t>
+  </si>
+  <si>
+    <t>11 sept</t>
+  </si>
+  <si>
+    <t>12 sept</t>
+  </si>
+  <si>
+    <t>13 sept</t>
+  </si>
+  <si>
+    <t>Sopa de macarrones</t>
+  </si>
+  <si>
+    <t>Carne a las finas hierbas</t>
+  </si>
+  <si>
+    <t>Papa al vapor</t>
+  </si>
+  <si>
+    <t>Verduras al gratín</t>
+  </si>
+  <si>
+    <t>Arroz al maní</t>
+  </si>
+  <si>
+    <t>Sopa de cebada perlada</t>
+  </si>
+  <si>
+    <t>Fricasé de pollo y champiñones</t>
+  </si>
+  <si>
+    <t>Ensalada mil islas</t>
+  </si>
+  <si>
+    <t>Arroz malteado</t>
+  </si>
+  <si>
+    <t>Papa crisper</t>
+  </si>
+  <si>
+    <t>Sopa de torrejas</t>
+  </si>
+  <si>
+    <t>Chuleta de cerdo a la plancha</t>
+  </si>
+  <si>
+    <t>Mini yuca dorada</t>
+  </si>
+  <si>
+    <t>Pepinos a la criolla</t>
+  </si>
+  <si>
+    <t>Arroz con maicitos</t>
+  </si>
+  <si>
+    <t>Sopa de colicero</t>
+  </si>
+  <si>
+    <t>Milanesa de pollo con ajonjolí</t>
+  </si>
+  <si>
+    <t>Ensalada oriental</t>
+  </si>
+  <si>
+    <t>Sopa de tortilla de maíz</t>
+  </si>
+  <si>
+    <t>Filete de tilapia</t>
+  </si>
+  <si>
+    <t>En salsa marinera</t>
+  </si>
+  <si>
+    <t>Plátano chip</t>
+  </si>
+  <si>
+    <t>Ensalada romana</t>
+  </si>
+  <si>
+    <t>Arroz palito</t>
+  </si>
+  <si>
+    <t>Sopa de mazorca chiquita</t>
+  </si>
+  <si>
+    <t>Sobrebarriga al horno</t>
+  </si>
+  <si>
+    <t>Papa chorreada</t>
+  </si>
+  <si>
+    <t>Ensalada con aguacate</t>
+  </si>
+  <si>
+    <t>Arroz con pollo</t>
+  </si>
+  <si>
+    <t>Plátano al horno</t>
+  </si>
+  <si>
+    <t>Con queso y bocadillo</t>
+  </si>
+  <si>
+    <t>Ensalada al huevo</t>
   </si>
 </sst>
 </file>
@@ -307,7 +307,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -330,11 +330,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE4D6C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE4D6C6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -359,6 +370,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -701,14 +715,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -717,14 +731,14 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -733,14 +747,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -749,14 +763,14 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -765,14 +779,14 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -781,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
@@ -797,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
@@ -813,14 +827,14 @@
         <v>9</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="4" t="s">
-        <v>50</v>
+      <c r="E9" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -829,14 +843,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -845,14 +859,14 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -861,7 +875,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
@@ -877,7 +891,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>10</v>
@@ -893,7 +907,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
@@ -909,7 +923,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>10</v>
@@ -925,7 +939,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
@@ -941,7 +955,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>10</v>
@@ -957,7 +971,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
@@ -973,14 +987,14 @@
         <v>12</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -989,14 +1003,14 @@
         <v>12</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F20" s="4"/>
     </row>
@@ -1005,14 +1019,14 @@
         <v>12</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F21" s="4"/>
     </row>
@@ -1021,14 +1035,14 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F22" s="4"/>
     </row>
@@ -1037,23 +1051,25 @@
         <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>10</v>
@@ -1069,7 +1085,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>10</v>
@@ -1085,14 +1101,14 @@
         <v>13</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="F26" s="4"/>
     </row>
@@ -1101,7 +1117,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>10</v>
@@ -1121,7 +1137,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>10</v>
@@ -1139,7 +1155,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>10</v>
@@ -1157,7 +1173,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>10</v>
@@ -1175,7 +1191,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>10</v>
@@ -1193,7 +1209,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>10</v>
@@ -1202,7 +1218,7 @@
         <v>20</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F32" s="4"/>
     </row>
@@ -1211,7 +1227,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>10</v>
@@ -1220,16 +1236,18 @@
         <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:6" ht="28" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>10</v>
@@ -1238,18 +1256,16 @@
         <v>20</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>10</v>
@@ -1257,9 +1273,7 @@
       <c r="D35" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -1267,14 +1281,14 @@
         <v>22</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F36" s="4"/>
     </row>
@@ -1283,14 +1297,14 @@
         <v>22</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -1299,14 +1313,14 @@
         <v>22</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F38" s="4"/>
     </row>
@@ -1315,14 +1329,14 @@
         <v>22</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F39" s="4"/>
     </row>
@@ -1331,14 +1345,14 @@
         <v>22</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="F40" s="4"/>
     </row>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62F62967-4820-4C25-89C4-740852937874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7206C0DB-6400-4FEB-9AEC-A57850187B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="24330" windowHeight="13110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -26,14 +26,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="84">
+  <si>
+    <t>Día</t>
+  </si>
   <si>
     <t>Menú de Lisboa 134 — Golconda</t>
   </si>
   <si>
-    <t>Día</t>
-  </si>
-  <si>
     <t>Fecha</t>
   </si>
   <si>
@@ -43,127 +43,151 @@
     <t>Opción</t>
   </si>
   <si>
+    <t>Plato</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
     <t>IMPORTANTE: este archivo es SOLO del punto Lisboa 134. El otro punto tiene su propio archivo.</t>
   </si>
   <si>
-    <t>Plato</t>
-  </si>
-  <si>
-    <t>Descripción</t>
-  </si>
-  <si>
     <t>1) Cada FILA es un plato. Un plato por fila.</t>
   </si>
   <si>
     <t>2) «Día»: elígelo en la lista desplegable.</t>
   </si>
   <si>
+    <t>3) «Fecha»: la que se muestra (ej. 13 jul). Repítela en todas las filas de ese día.</t>
+  </si>
+  <si>
     <t>Lunes</t>
   </si>
   <si>
-    <t>3) «Fecha»: la que se muestra (ej. 13 jul). Repítela en todas las filas de ese día.</t>
-  </si>
-  <si>
     <t>4) «Festivo»: «Sí» solo si ese día cobra tarifa de domingo/festivo; si no, «No».</t>
   </si>
   <si>
     <t>5) «Plato»: el nombre del plato.</t>
   </si>
   <si>
-    <t>14 sept</t>
-  </si>
-  <si>
     <t>6) «Descripción»: nota corta que aparece DEBAJO del plato (opcional).</t>
   </si>
   <si>
+    <t>Días con dos menús (como el sábado)</t>
+  </si>
+  <si>
+    <t>• Llena «Opción» con «Opción 1» y «Opción 2». Si hay un solo menú, déjala vacía.</t>
+  </si>
+  <si>
+    <t>21 sept</t>
+  </si>
+  <si>
+    <t>Publicar</t>
+  </si>
+  <si>
+    <t>Guarda con el nombre menu-lisboa.xlsx y súbelo a GitHub reemplazando el anterior.</t>
+  </si>
+  <si>
+    <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Días con dos menús (como el sábado)</t>
-  </si>
-  <si>
-    <t>• Llena «Opción» con «Opción 1» y «Opción 2». Si hay un solo menú, déjala vacía.</t>
-  </si>
-  <si>
-    <t>Sopa de cuchuco de cebada</t>
-  </si>
-  <si>
-    <t>Publicar</t>
-  </si>
-  <si>
-    <t>Guarda con el nombre menu-lisboa.xlsx y súbelo a GitHub reemplazando el anterior.</t>
-  </si>
-  <si>
-    <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
-  </si>
-  <si>
-    <t>Carne encebollada</t>
-  </si>
-  <si>
-    <t>Ensalada campesina</t>
+    <t>Sopa de avena</t>
+  </si>
+  <si>
+    <t>Lomo de cerdo</t>
+  </si>
+  <si>
+    <t>En salsa stroganoff</t>
+  </si>
+  <si>
+    <t>Papa lionesa</t>
+  </si>
+  <si>
+    <t>Ensalada verde</t>
+  </si>
+  <si>
+    <t>Arroz con ajonjolí</t>
+  </si>
+  <si>
+    <t>Martes</t>
+  </si>
+  <si>
+    <t>22 sept</t>
+  </si>
+  <si>
+    <t>Sopa de arroz con menudencias</t>
+  </si>
+  <si>
+    <t>Lasagna mixta</t>
+  </si>
+  <si>
+    <t>Ensalada de verano</t>
+  </si>
+  <si>
+    <t>Papa a la francesa</t>
+  </si>
+  <si>
+    <t>Miércoles</t>
+  </si>
+  <si>
+    <t>23 sept</t>
+  </si>
+  <si>
+    <t>Sopa de conchitas</t>
+  </si>
+  <si>
+    <t>Milanesa de cerdo</t>
+  </si>
+  <si>
+    <t>Papa al perejil</t>
+  </si>
+  <si>
+    <t>Ensalada con mostaza dijon</t>
+  </si>
+  <si>
+    <t>Arroz al cebollín</t>
+  </si>
+  <si>
+    <t>Jueves</t>
+  </si>
+  <si>
+    <t>24 sept</t>
+  </si>
+  <si>
+    <t>Crema de espinaca</t>
+  </si>
+  <si>
+    <t>Pollo a la naranja</t>
   </si>
   <si>
     <t>Arroz blanco</t>
   </si>
   <si>
-    <t>Martes</t>
-  </si>
-  <si>
-    <t>15 sept</t>
-  </si>
-  <si>
-    <t>Sopa de minestrone</t>
-  </si>
-  <si>
-    <t>Papa crisper</t>
-  </si>
-  <si>
-    <t>Arroz a las finas hierbas</t>
-  </si>
-  <si>
-    <t>Miércoles</t>
-  </si>
-  <si>
-    <t>16 sept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arroz mixto </t>
-  </si>
-  <si>
-    <t>Chop suey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollitos de piña </t>
-  </si>
-  <si>
-    <t>En salsa agridulce</t>
-  </si>
-  <si>
-    <t>Jueves</t>
-  </si>
-  <si>
-    <t>17 sept</t>
-  </si>
-  <si>
-    <t>Sopa de lentejas</t>
-  </si>
-  <si>
-    <t>Pollo a la criolla</t>
-  </si>
-  <si>
     <t>Viernes</t>
   </si>
   <si>
-    <t>18 sept</t>
-  </si>
-  <si>
-    <t>Sopa de sancocho</t>
+    <t>25 sept</t>
+  </si>
+  <si>
+    <t>Sopa de arracacha</t>
+  </si>
+  <si>
+    <t>En salsa de coco</t>
+  </si>
+  <si>
+    <t>Ensalada con aguacate, pepino cohombro y tomate</t>
+  </si>
+  <si>
+    <t>Arroz pajarito</t>
   </si>
   <si>
     <t>Sábado</t>
   </si>
   <si>
-    <t>19 sept</t>
+    <t>26 sept</t>
   </si>
   <si>
     <t>Opción 1</t>
@@ -187,80 +211,80 @@
     <t>Sopa de ajiaco</t>
   </si>
   <si>
-    <t>Carne a la cerveza</t>
-  </si>
-  <si>
-    <t>Cascos de papa dorada</t>
-  </si>
-  <si>
-    <t>Ensalada del sol</t>
+    <t>Alitas de pollo a la broaster</t>
+  </si>
+  <si>
+    <t>Papa alemana</t>
+  </si>
+  <si>
+    <t>Ensalada hawaiana</t>
   </si>
   <si>
     <t>Domingo</t>
   </si>
   <si>
-    <t>20 sept</t>
+    <t>27 sept</t>
   </si>
   <si>
     <t>Sí</t>
   </si>
   <si>
-    <t>Sopa de cascabeles</t>
-  </si>
-  <si>
-    <t>Papa a la griega</t>
-  </si>
-  <si>
-    <t>Ensalada cherry</t>
-  </si>
-  <si>
-    <t>Arroz al perejil</t>
-  </si>
-  <si>
-    <t>Torta de plátano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollo de pollo </t>
-  </si>
-  <si>
-    <t>En salsa de champiñones</t>
-  </si>
-  <si>
-    <t>Ensalada césar</t>
-  </si>
-  <si>
-    <t>Crema de zanahoría</t>
-  </si>
-  <si>
-    <t>Pollo, res y cerdo</t>
-  </si>
-  <si>
-    <t>Monedas de plátano</t>
+    <t>Bandeja paisa</t>
+  </si>
+  <si>
+    <t>Sopa de maíz pintado</t>
+  </si>
+  <si>
+    <t>Carne de res / Pollo / Chuleta de cerdo</t>
+  </si>
+  <si>
+    <t>Elige tu proteína</t>
   </si>
   <si>
     <t>Ensalada mixta a la vinagreta</t>
   </si>
   <si>
-    <t>Arroz al pimentón</t>
-  </si>
-  <si>
-    <t>Hígado a la plancha</t>
-  </si>
-  <si>
-    <t>Yuca a la criolla</t>
-  </si>
-  <si>
-    <t>Ensalada fantasía</t>
-  </si>
-  <si>
-    <t>Pierna pernil mediterráneo</t>
+    <t>Arroz Blanco</t>
+  </si>
+  <si>
+    <t>Con pollo y bolognesa</t>
+  </si>
+  <si>
+    <t>Con salsa de piña</t>
+  </si>
+  <si>
+    <t>Papa hash brown</t>
+  </si>
+  <si>
+    <t>Soufflé de berenjena</t>
+  </si>
+  <si>
+    <t>Filete de mojarra</t>
+  </si>
+  <si>
+    <t>Croqueta de yuca</t>
+  </si>
+  <si>
+    <t>A la vinagreta</t>
+  </si>
+  <si>
+    <t>9 acompañamientos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carne molina, chicharrón, chorizo, fríjoles, huevo, plátano, aguacate, arepa y arroz blanco </t>
+  </si>
+  <si>
+    <t>Plátano maduro</t>
+  </si>
+  <si>
+    <t>Pan francés con ajo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,14 +293,14 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FFF25238"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <color rgb="FFF25238"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -300,6 +324,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -354,13 +384,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -385,6 +415,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F999"/>
+  <dimension ref="A1:F1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -612,332 +645,332 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="8" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="8" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="9" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="8" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="8" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>36</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="8" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F20" s="8"/>
     </row>
@@ -949,381 +982,463 @@
         <v>42</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="8" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="8"/>
+        <v>77</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="8" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>46</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D26" s="7"/>
       <c r="E26" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>48</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F27" s="8"/>
+        <v>55</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="F30" s="8"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F32" s="8"/>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>25</v>
+        <v>59</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="F34" s="8"/>
     </row>
     <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>59</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="7"/>
+        <v>66</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="E36" s="8" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F36" s="8"/>
     </row>
     <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="7"/>
+        <v>66</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="E37" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F37" s="8"/>
+        <v>80</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="8"/>
+        <v>66</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="8"/>
+      <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F39" s="8"/>
+        <v>66</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="A40" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
+      <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="5"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="8"/>
+      <c r="A41" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>68</v>
+      </c>
       <c r="F41" s="8"/>
     </row>
     <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
+      <c r="A42" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="8"/>
+      <c r="A43" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="F43" s="8"/>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="5"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="8"/>
+      <c r="A44" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>71</v>
+      </c>
       <c r="F44" s="8"/>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
+      <c r="A45" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="8"/>
     </row>
     <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
+      <c r="A46" s="5"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
     </row>
     <row r="47" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="A47" s="5"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
     </row>
     <row r="48" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
+      <c r="A48" s="5"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
     </row>
     <row r="49" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="11"/>
@@ -3080,23 +3195,39 @@
       <c r="C399" s="11"/>
       <c r="D399" s="11"/>
     </row>
-    <row r="400" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="400" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A400" s="11"/>
+      <c r="C400" s="11"/>
+      <c r="D400" s="11"/>
+    </row>
+    <row r="401" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A401" s="11"/>
+      <c r="C401" s="11"/>
+      <c r="D401" s="11"/>
+    </row>
+    <row r="402" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A402" s="11"/>
+      <c r="C402" s="11"/>
+      <c r="D402" s="11"/>
+    </row>
+    <row r="403" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A403" s="11"/>
+      <c r="C403" s="11"/>
+      <c r="D403" s="11"/>
+    </row>
+    <row r="404" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="405" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="406" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="407" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="408" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="409" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="410" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="411" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="412" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="413" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="414" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="415" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="416" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -3680,15 +3811,19 @@
     <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D399" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D403" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C399" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C403" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="A2:A399" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A403" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3707,8 +3842,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3716,7 +3851,7 @@
     </row>
     <row r="3" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3734,7 +3869,7 @@
     </row>
     <row r="7" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3749,7 +3884,7 @@
     </row>
     <row r="10" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3757,12 +3892,12 @@
     </row>
     <row r="12" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3770,17 +3905,17 @@
     </row>
     <row r="15" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{7206C0DB-6400-4FEB-9AEC-A57850187B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6438649F-D4F0-4A0C-8EC7-DC0CA6A05DCB}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="8_{7206C0DB-6400-4FEB-9AEC-A57850187B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FA089F6-9504-426F-8931-3D939E3B1327}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="76">
   <si>
     <t>Día</t>
   </si>
@@ -91,18 +91,12 @@
     <t>No</t>
   </si>
   <si>
-    <t>Sopa de avena</t>
-  </si>
-  <si>
     <t>Martes</t>
   </si>
   <si>
     <t>Miércoles</t>
   </si>
   <si>
-    <t>Arroz al cebollín</t>
-  </si>
-  <si>
     <t>Jueves</t>
   </si>
   <si>
@@ -142,128 +136,131 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>28 sept</t>
-  </si>
-  <si>
-    <t>29 sept</t>
-  </si>
-  <si>
-    <t>30 sept</t>
-  </si>
-  <si>
-    <t>1 oct</t>
-  </si>
-  <si>
-    <t>2 oct</t>
-  </si>
-  <si>
-    <t>3 oct</t>
-  </si>
-  <si>
-    <t>4 oct</t>
-  </si>
-  <si>
-    <t>Sopa de verduras</t>
-  </si>
-  <si>
-    <t>Carne al vino</t>
-  </si>
-  <si>
-    <t>Croquetas de papa</t>
-  </si>
-  <si>
-    <t>Ensalada waldorf</t>
-  </si>
-  <si>
-    <t>Arroz almendrado</t>
-  </si>
-  <si>
-    <t>Crema zuchinni</t>
-  </si>
-  <si>
-    <t>Soufflé de pollo y atún</t>
-  </si>
-  <si>
-    <t>Papa chip</t>
-  </si>
-  <si>
-    <t>Ensalada de huevo moscovita</t>
-  </si>
-  <si>
-    <t>Sopa de torrejas</t>
-  </si>
-  <si>
-    <t>Carne de res a la plancha</t>
-  </si>
-  <si>
-    <t>Plátano al horno</t>
-  </si>
-  <si>
-    <t>Sidra en salsa al pimentón</t>
-  </si>
-  <si>
-    <t>Arroz con zanahoria</t>
-  </si>
-  <si>
-    <t>Sopa de cuchuco de trigo</t>
-  </si>
-  <si>
-    <t>Pollo al horno</t>
-  </si>
-  <si>
-    <t>Papa salada</t>
-  </si>
-  <si>
-    <t>Guacamole</t>
-  </si>
-  <si>
-    <t>Arroz con verduras</t>
-  </si>
-  <si>
-    <t>Sopa de colicero</t>
-  </si>
-  <si>
-    <t>Bistec a caballo</t>
-  </si>
-  <si>
-    <t>Bananitos al horno</t>
-  </si>
-  <si>
-    <t>En salsa de naranja</t>
-  </si>
-  <si>
-    <t>Ensalada multicolor</t>
-  </si>
-  <si>
-    <t>Bolitas de res</t>
-  </si>
-  <si>
-    <t>En salsa napolitana</t>
-  </si>
-  <si>
-    <t>Yuca dorada</t>
-  </si>
-  <si>
-    <t>Soufflé de acelgas</t>
-  </si>
-  <si>
-    <t>Pierna pernil a la broaster</t>
-  </si>
-  <si>
-    <t>Papas horneadas al limón</t>
-  </si>
-  <si>
-    <t>Ensalada de pepino cohombro</t>
-  </si>
-  <si>
-    <t>Con yogurt</t>
+    <t>5 oct</t>
+  </si>
+  <si>
+    <t>Sopa de mazorca</t>
+  </si>
+  <si>
+    <t>Carne desmechada</t>
+  </si>
+  <si>
+    <t>Patacón</t>
+  </si>
+  <si>
+    <t>Ensalada veraniega</t>
+  </si>
+  <si>
+    <t>Arroz con caraota</t>
+  </si>
+  <si>
+    <t>6 oct</t>
+  </si>
+  <si>
+    <t>Sopa de cebada perlada</t>
+  </si>
+  <si>
+    <t>Pollo a la americana</t>
+  </si>
+  <si>
+    <t>Papa a la francesa</t>
+  </si>
+  <si>
+    <t>Verduras al gratín</t>
+  </si>
+  <si>
+    <t>Arroz al perejíl</t>
+  </si>
+  <si>
+    <t>7 oct</t>
+  </si>
+  <si>
+    <t>Sopa de sancocho</t>
+  </si>
+  <si>
+    <t>Lengua Napolitana</t>
+  </si>
+  <si>
+    <t>Puré de papa mixta</t>
+  </si>
+  <si>
+    <t>Ensalada arcoíris</t>
+  </si>
+  <si>
+    <t>8 oct</t>
+  </si>
+  <si>
+    <t>Sopa de mazamorra chiquita</t>
+  </si>
+  <si>
+    <t>Pollo a la jardinera</t>
+  </si>
+  <si>
+    <t>Torta de mazorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensalada de pepino cohombro, tomate y remolacha </t>
+  </si>
+  <si>
+    <t>A la vinagreta</t>
+  </si>
+  <si>
+    <t>9 oct</t>
+  </si>
+  <si>
+    <t>Sopa de tortilla de huevo</t>
+  </si>
+  <si>
+    <t>Filete de mojarra</t>
+  </si>
+  <si>
+    <t>En salsa de camarones</t>
+  </si>
+  <si>
+    <t>Enyucado</t>
+  </si>
+  <si>
+    <t>Ensalada romana</t>
+  </si>
+  <si>
+    <t>Arroz con maicitos</t>
+  </si>
+  <si>
+    <t>10 oct</t>
+  </si>
+  <si>
+    <t>Milanesa de pollo con ajonjolí</t>
+  </si>
+  <si>
+    <t>Papa al vapor</t>
+  </si>
+  <si>
+    <t>Ensalada de melón</t>
+  </si>
+  <si>
+    <t>Con vinagreta oriental</t>
+  </si>
+  <si>
+    <t>11 oct</t>
+  </si>
+  <si>
+    <t>Sopa de minestrone</t>
+  </si>
+  <si>
+    <t>Costillas de cerdo al BBQ</t>
+  </si>
+  <si>
+    <t>Papa asada</t>
+  </si>
+  <si>
+    <t>Verduras salteadas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,12 +300,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -363,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -394,9 +385,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,6 +400,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -648,14 +640,14 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="8" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F2" s="8"/>
     </row>
@@ -664,14 +656,14 @@
         <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="8" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F3" s="8"/>
     </row>
@@ -680,14 +672,14 @@
         <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F4" s="8"/>
     </row>
@@ -696,14 +688,14 @@
         <v>11</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F5" s="8"/>
     </row>
@@ -712,586 +704,586 @@
         <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="8" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="8" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="8" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="8" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F23" s="8"/>
+        <v>61</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>67</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F25" s="8"/>
     </row>
     <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="8" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="F26" s="8"/>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="8" t="s">
         <v>29</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F28" s="8"/>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F29" s="8"/>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F30" s="8"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F31" s="8"/>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>70</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F32" s="8"/>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F33" s="8"/>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="8" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="F36" s="8"/>
     </row>
     <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="12"/>
+      <c r="F37" s="8"/>
     </row>
     <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="12"/>
+      <c r="F38" s="8"/>
     </row>
     <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>76</v>
-      </c>
+      <c r="F39" s="8"/>
     </row>
     <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="12"/>
+      <c r="F40" s="8"/>
     </row>
     <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{7206C0DB-6400-4FEB-9AEC-A57850187B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B62A95A4-FC99-4562-B1B2-D5C08473F248}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{7206C0DB-6400-4FEB-9AEC-A57850187B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06A86EAD-D3C0-47B1-95E6-E0ADB604D015}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="85">
   <si>
     <t>Día</t>
   </si>
@@ -196,9 +196,6 @@
     <t>Costilla de res</t>
   </si>
   <si>
-    <t>Yuca - plátano - mazorca</t>
-  </si>
-  <si>
     <t>Guacamole</t>
   </si>
   <si>
@@ -220,9 +217,6 @@
     <t>En salsa provenzal</t>
   </si>
   <si>
-    <t>Soufle de papa</t>
-  </si>
-  <si>
     <t>Ensalada florentina</t>
   </si>
   <si>
@@ -281,6 +275,12 @@
   </si>
   <si>
     <t>Arroz al perejíl</t>
+  </si>
+  <si>
+    <t>Yuca - Plátano - Mazorca</t>
+  </si>
+  <si>
+    <t>Soufflé de papa</t>
   </si>
 </sst>
 </file>
@@ -382,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -411,6 +411,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F998"/>
+  <dimension ref="A1:F996"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -894,7 +897,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -912,7 +915,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F16" s="9"/>
     </row>
@@ -948,7 +951,7 @@
         <v>32</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F18" s="9"/>
     </row>
@@ -986,7 +989,7 @@
         <v>32</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F20" s="9"/>
     </row>
@@ -1000,11 +1003,9 @@
       <c r="C21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="D21" s="8"/>
       <c r="E21" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" s="9"/>
     </row>
@@ -1018,9 +1019,7 @@
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="D22" s="8"/>
       <c r="E22" s="9" t="s">
         <v>24</v>
       </c>
@@ -1031,14 +1030,14 @@
         <v>23</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F23" s="9"/>
     </row>
@@ -1047,17 +1046,17 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1065,14 +1064,14 @@
         <v>23</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="9" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F25" s="9"/>
     </row>
@@ -1081,14 +1080,14 @@
         <v>23</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F26" s="9"/>
     </row>
@@ -1097,14 +1096,14 @@
         <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F27" s="9"/>
     </row>
@@ -1113,14 +1112,14 @@
         <v>25</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F28" s="9"/>
     </row>
@@ -1129,14 +1128,14 @@
         <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F29" s="9"/>
     </row>
@@ -1145,14 +1144,14 @@
         <v>25</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F30" s="9"/>
     </row>
@@ -1161,17 +1160,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="8"/>
       <c r="E31" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1179,14 +1177,13 @@
         <v>25</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="8"/>
       <c r="E32" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F32" s="9"/>
     </row>
@@ -1195,7 +1192,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>20</v>
@@ -1215,7 +1212,7 @@
         <v>26</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>20</v>
@@ -1233,7 +1230,7 @@
         <v>26</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>20</v>
@@ -1251,7 +1248,7 @@
         <v>26</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>20</v>
@@ -1269,7 +1266,7 @@
         <v>26</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>20</v>
@@ -1287,7 +1284,7 @@
         <v>26</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>20</v>
@@ -1296,7 +1293,7 @@
         <v>32</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F38" s="9"/>
     </row>
@@ -1305,7 +1302,7 @@
         <v>26</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>20</v>
@@ -1314,7 +1311,7 @@
         <v>32</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F39" s="9"/>
     </row>
@@ -1323,7 +1320,7 @@
         <v>26</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>20</v>
@@ -1332,10 +1329,10 @@
         <v>32</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1343,14 +1340,14 @@
         <v>34</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F41" s="9"/>
     </row>
@@ -1359,14 +1356,14 @@
         <v>34</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F42" s="9"/>
     </row>
@@ -1375,14 +1372,14 @@
         <v>34</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F43" s="9"/>
     </row>
@@ -1391,14 +1388,14 @@
         <v>34</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="8"/>
+      <c r="D44" s="5"/>
       <c r="E44" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F44" s="9"/>
     </row>
@@ -1407,14 +1404,14 @@
         <v>34</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D45" s="8"/>
+      <c r="D45" s="5"/>
       <c r="E45" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F45" s="9"/>
     </row>
@@ -3173,16 +3170,8 @@
       <c r="C396" s="5"/>
       <c r="D396" s="5"/>
     </row>
-    <row r="397" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A397" s="5"/>
-      <c r="C397" s="5"/>
-      <c r="D397" s="5"/>
-    </row>
-    <row r="398" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="5"/>
-      <c r="C398" s="5"/>
-      <c r="D398" s="5"/>
-    </row>
+    <row r="397" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="399" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="400" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3781,18 +3770,16 @@
     <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="D2:D398" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C398" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C396" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="A2:A398" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A396" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D30 D33:D396" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/menu-lisboa.xlsx
+++ b/menu-lisboa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{7206C0DB-6400-4FEB-9AEC-A57850187B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06A86EAD-D3C0-47B1-95E6-E0ADB604D015}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{7206C0DB-6400-4FEB-9AEC-A57850187B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75B8F4A8-4B7F-4AE7-B066-774CA5AD5019}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="75">
   <si>
     <t>Día</t>
   </si>
@@ -136,158 +136,128 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Carne de res / Chuleta de cerdo / Pollo</t>
-  </si>
-  <si>
-    <t>Elige tu proteína</t>
-  </si>
-  <si>
-    <t>19 oct</t>
-  </si>
-  <si>
-    <t>Sopa de macarrones</t>
-  </si>
-  <si>
-    <t>Muchacho relleno</t>
-  </si>
-  <si>
-    <t>En salsa de maracuya</t>
-  </si>
-  <si>
-    <t>Papa al gratin</t>
-  </si>
-  <si>
-    <t>Ensalada al pesto</t>
-  </si>
-  <si>
-    <t>Arroz a las finas hierbas</t>
-  </si>
-  <si>
-    <t>20 oct</t>
-  </si>
-  <si>
-    <t>Crema de ahuyama</t>
-  </si>
-  <si>
-    <t>Pollo oriental</t>
-  </si>
-  <si>
-    <t>En salsa de mango</t>
-  </si>
-  <si>
-    <t>Papa en cascos</t>
-  </si>
-  <si>
-    <t>Ensalada cherry</t>
-  </si>
-  <si>
-    <t>Arroz con hilos de espinaca</t>
-  </si>
-  <si>
-    <t>21 oct</t>
-  </si>
-  <si>
-    <t>Entero</t>
-  </si>
-  <si>
-    <t>Consome</t>
-  </si>
-  <si>
-    <t>Costilla de res</t>
-  </si>
-  <si>
-    <t>Guacamole</t>
-  </si>
-  <si>
-    <t>Sopa de arracacha</t>
-  </si>
-  <si>
-    <t>Yuca ó platano</t>
-  </si>
-  <si>
-    <t>22 oct</t>
-  </si>
-  <si>
-    <t>Sopa de avena</t>
-  </si>
-  <si>
-    <t>Pernil de pollo</t>
-  </si>
-  <si>
-    <t>En salsa provenzal</t>
-  </si>
-  <si>
-    <t>Ensalada florentina</t>
-  </si>
-  <si>
-    <t>Arroz verde</t>
-  </si>
-  <si>
-    <t>23 oct</t>
-  </si>
-  <si>
-    <t>Sopa de colicero</t>
-  </si>
-  <si>
-    <t>Mojarra frita</t>
-  </si>
-  <si>
-    <t>Ensalada rusa</t>
-  </si>
-  <si>
-    <t>Tomate, aguacate y pepino cohombro</t>
-  </si>
-  <si>
     <t>A la vinagreta</t>
   </si>
   <si>
-    <t>Arroz con maicitos</t>
-  </si>
-  <si>
-    <t>24 oct</t>
-  </si>
-  <si>
-    <t>Arroz mixto</t>
-  </si>
-  <si>
-    <t>Chop suey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollitos de piña </t>
-  </si>
-  <si>
-    <t>En salsa agridulce</t>
-  </si>
-  <si>
-    <t>Crema de espárragos</t>
-  </si>
-  <si>
-    <t>25 oct</t>
-  </si>
-  <si>
-    <t>Pollo a la naranja</t>
-  </si>
-  <si>
-    <t>Papa hash brown</t>
-  </si>
-  <si>
-    <t>Soufflé de Berenjena</t>
-  </si>
-  <si>
-    <t>Arroz al perejíl</t>
-  </si>
-  <si>
-    <t>Yuca - Plátano - Mazorca</t>
-  </si>
-  <si>
-    <t>Soufflé de papa</t>
+    <t>26 oct</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco de maíz</t>
+  </si>
+  <si>
+    <t>Goulash</t>
+  </si>
+  <si>
+    <t>Puré de papa</t>
+  </si>
+  <si>
+    <t>Habichuelas rancheras</t>
+  </si>
+  <si>
+    <t>27 oct</t>
+  </si>
+  <si>
+    <t>Sopa de minestrone</t>
+  </si>
+  <si>
+    <t>Pollo a la vizcaína</t>
+  </si>
+  <si>
+    <t>Cascos de papa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensalada de melón </t>
+  </si>
+  <si>
+    <t>Con vinagreta oriental</t>
+  </si>
+  <si>
+    <t>Arroz al cebollín</t>
+  </si>
+  <si>
+    <t>28 oct</t>
+  </si>
+  <si>
+    <t>Sopa de torrejas</t>
+  </si>
+  <si>
+    <t>Pulpa de cerdo a la plancha</t>
+  </si>
+  <si>
+    <t>Plátano al horno</t>
+  </si>
+  <si>
+    <t>Pepinos rellenos con verduras</t>
+  </si>
+  <si>
+    <t>29 oct</t>
+  </si>
+  <si>
+    <t>Sopa de patacón</t>
+  </si>
+  <si>
+    <t>Pollo al BBQ</t>
+  </si>
+  <si>
+    <t>Papa postiza</t>
+  </si>
+  <si>
+    <t>Ensalada verde</t>
+  </si>
+  <si>
+    <t>Arroz con ajonjolí</t>
+  </si>
+  <si>
+    <t>30 oct</t>
+  </si>
+  <si>
+    <t>Sopa de mazorca</t>
+  </si>
+  <si>
+    <t>Soufflé de carne</t>
+  </si>
+  <si>
+    <t>Mini yuca dorada</t>
+  </si>
+  <si>
+    <t>Zanahoria y brocolí vicky</t>
+  </si>
+  <si>
+    <t>31 oct</t>
+  </si>
+  <si>
+    <t>Pollo a la criolla</t>
+  </si>
+  <si>
+    <t>Torta de plátano</t>
+  </si>
+  <si>
+    <t>Ensalada Mixta</t>
+  </si>
+  <si>
+    <t>1 nov</t>
+  </si>
+  <si>
+    <t>Sopa de verduras</t>
+  </si>
+  <si>
+    <t>Carne al vino</t>
+  </si>
+  <si>
+    <t>Croquetas de papa</t>
+  </si>
+  <si>
+    <t>Ensalada Waldorf</t>
+  </si>
+  <si>
+    <t>Arroz almendrado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,6 +298,11 @@
       <color rgb="FF222222"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -382,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -412,9 +387,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -669,15 +648,15 @@
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>38</v>
+      <c r="B2" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" s="9"/>
     </row>
@@ -685,33 +664,31 @@
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
+      <c r="B3" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>41</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>38</v>
+      <c r="B4" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F4" s="9"/>
     </row>
@@ -719,15 +696,15 @@
       <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>38</v>
+      <c r="B5" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F5" s="9"/>
     </row>
@@ -735,15 +712,15 @@
       <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>38</v>
+      <c r="B6" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="9" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F6" s="9"/>
     </row>
@@ -751,15 +728,15 @@
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>45</v>
+      <c r="B7" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F7" s="9"/>
     </row>
@@ -767,33 +744,31 @@
       <c r="A8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>45</v>
+      <c r="B8" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>48</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>45</v>
+      <c r="B9" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F9" s="9"/>
     </row>
@@ -801,31 +776,33 @@
       <c r="A10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>45</v>
+      <c r="B10" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="9"/>
+        <v>46</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>45</v>
+      <c r="B11" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F11" s="9"/>
     </row>
@@ -833,17 +810,15 @@
       <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>52</v>
+      <c r="B12" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="D12" s="8"/>
       <c r="E12" s="9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -851,17 +826,15 @@
       <c r="A13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>52</v>
+      <c r="B13" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="D13" s="8"/>
       <c r="E13" s="9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F13" s="9"/>
     </row>
@@ -869,17 +842,15 @@
       <c r="A14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>52</v>
+      <c r="B14" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="D14" s="8"/>
       <c r="E14" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F14" s="9"/>
     </row>
@@ -887,17 +858,15 @@
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>52</v>
+      <c r="B15" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="D15" s="8"/>
       <c r="E15" s="9" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -905,89 +874,77 @@
       <c r="A16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>52</v>
+      <c r="B16" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="D16" s="8"/>
       <c r="E16" s="9" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>27</v>
-      </c>
+      <c r="D17" s="8"/>
       <c r="E17" s="9" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="F17" s="9"/>
     </row>
     <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="D18" s="8"/>
       <c r="E18" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F18" s="9"/>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="D19" s="8"/>
       <c r="E19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>37</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>32</v>
-      </c>
+      <c r="D20" s="8"/>
       <c r="E20" s="9" t="s">
         <v>58</v>
       </c>
@@ -995,195 +952,205 @@
     </row>
     <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F21" s="9"/>
     </row>
     <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>52</v>
+        <v>25</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="9" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>59</v>
+        <v>25</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>59</v>
+        <v>25</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>62</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>59</v>
+        <v>25</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="8"/>
       <c r="E25" s="9" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>59</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="8"/>
       <c r="E26" s="9" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>59</v>
+        <v>26</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="8"/>
+      <c r="D27" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="E27" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="8"/>
+      <c r="D28" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="E28" s="9" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="F28" s="9"/>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="8"/>
+      <c r="D29" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="E29" s="9" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="F29" s="9"/>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="8"/>
+      <c r="D30" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="E30" s="9" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="F30" s="9"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>20</v>
       </c>
+      <c r="D31" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="E31" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>70</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F31" s="9"/>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>20</v>
       </c>
+      <c r="D32" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="E32" s="9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F32" s="9"/>
     </row>
@@ -1191,228 +1158,175 @@
       <c r="A33" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>72</v>
+      <c r="B33" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>29</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F33" s="9"/>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>72</v>
+      <c r="B34" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" s="9"/>
+        <v>68</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>72</v>
+      <c r="B35" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F35" s="9"/>
     </row>
     <row r="36" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>27</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D36" s="8"/>
       <c r="E36" s="9" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F36" s="9"/>
     </row>
     <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>32</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D37" s="8"/>
       <c r="E37" s="9" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="F37" s="9"/>
     </row>
     <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="13"/>
+      <c r="E38" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>73</v>
       </c>
       <c r="F38" s="9"/>
     </row>
     <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>32</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="13"/>
       <c r="E39" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>32</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="13"/>
       <c r="E40" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A41" s="7"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="8"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="9" t="s">
-        <v>77</v>
-      </c>
+      <c r="E41" s="9"/>
       <c r="F41" s="9"/>
     </row>
     <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A42" s="7"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="9" t="s">
-        <v>79</v>
-      </c>
+      <c r="E42" s="9"/>
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>35</v>
-      </c>
+      <c r="A43" s="7"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="8"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="9" t="s">
-        <v>80</v>
-      </c>
+      <c r="E43" s="9"/>
       <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="A44" s="7"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="11"/>
       <c r="D44" s="5"/>
-      <c r="E44" s="9" t="s">
-        <v>81</v>
-      </c>
+      <c r="E44" s="9"/>
       <c r="F44" s="9"/>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>35</v>
-      </c>
+      <c r="A45" s="7"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="11"/>
       <c r="D45" s="5"/>
-      <c r="E45" s="9" t="s">
-        <v>82</v>
-      </c>
+      <c r="E45" s="9"/>
       <c r="F45" s="9"/>
     </row>
     <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3778,7 +3692,7 @@
     <dataValidation type="list" allowBlank="1" sqref="A2:A396" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D30 D33:D396" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D27:D396 D2:D24" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>
